--- a/cloud_state/offres_suivi.xlsx
+++ b/cloud_state/offres_suivi.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Offres" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offres" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Offres'!$A$1:$AB$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Offres'!$A$1:$AB$17</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB16"/>
+  <dimension ref="A1:AB17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -460,7 +460,7 @@
     <col width="21" customWidth="1" min="15" max="15"/>
     <col width="19" customWidth="1" min="16" max="16"/>
     <col width="57" customWidth="1" min="17" max="17"/>
-    <col width="29" customWidth="1" min="18" max="18"/>
+    <col width="35" customWidth="1" min="18" max="18"/>
     <col width="26" customWidth="1" min="19" max="19"/>
     <col width="13" customWidth="1" min="20" max="20"/>
     <col width="60" customWidth="1" min="21" max="21"/>
@@ -2150,8 +2150,104 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21T11:40:47</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>-8074488563249637161</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Jooble</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Développeur php full stack - h/f</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Altagile</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Sennecey-lès-Dijon, 21800</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>Temps plein</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr"/>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr"/>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr"/>
+      <c r="O17" s="2" t="inlineStr"/>
+      <c r="P17" s="2" t="inlineStr"/>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>JavaScript, React</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21T09:05:14.6248696+00:00</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr"/>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>Offre conservee: cible front-end, WordPress, webdesign, UI/UX ou graphisme web.</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>À vérifier</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>À vérifier: score 65/100 grâce à technologies: javascript, react, web; domaine_metier: wordpress, front-end, ui, ux, design, webdesign, graphisme; localisation: dijon.</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>technologies=35; titre=0; domaine_metier=15; localisation=15; teletravail=0; contrat=0</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>JavaScript, React</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr"/>
+      <c r="AB17" s="3" t="inlineStr">
+        <is>
+          <t>https://fr.jooble.org/jdp/-8074488563249637161</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AB16"/>
+  <autoFilter ref="A1:AB17"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB3" r:id="rId2"/>
@@ -2168,6 +2264,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB15" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB17" r:id="rId16"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/cloud_state/offres_suivi.xlsx
+++ b/cloud_state/offres_suivi.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offres" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Offres'!$A$1:$AB$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Offres'!$A$1:$AB$18</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -440,14 +440,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB17"/>
+  <dimension ref="A1:AB18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="33" customWidth="1" min="5" max="5"/>
+    <col width="36" customWidth="1" min="5" max="5"/>
     <col width="28" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="25" customWidth="1" min="8" max="8"/>
@@ -2246,8 +2246,110 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-27T11:53:30</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>7773417443002480443</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Jooble</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Développeur frontend angular</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>PROACTIVE RH - TERTIAIRE ET CADRES</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Dijon</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>Temps plein</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr"/>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>3 170 € a 3 570 €</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="n">
+        <v>3170</v>
+      </c>
+      <c r="L18" s="2" t="n">
+        <v>3570</v>
+      </c>
+      <c r="M18" s="2" t="n">
+        <v>3370</v>
+      </c>
+      <c r="N18" s="2" t="inlineStr"/>
+      <c r="O18" s="2" t="inlineStr"/>
+      <c r="P18" s="2" t="inlineStr"/>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-27T01:28:50.0971378+00:00</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr"/>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>Offre conservee: cible front-end, WordPress, webdesign, UI/UX ou graphisme web.</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>À vérifier</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>À vérifier: score 75/100 grâce à technologies: developpeur front-end, front-end; titre: frontend; domaine_metier: wordpress, frontend, front-end, ui, ux, design, webdesign, graphisme; localisation: dijon.</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
+        <is>
+          <t>technologies=30; titre=15; domaine_metier=15; localisation=15; teletravail=0; contrat=0</t>
+        </is>
+      </c>
+      <c r="Z18" s="2" t="inlineStr">
+        <is>
+          <t>developpeur front-end</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr"/>
+      <c r="AB18" s="3" t="inlineStr">
+        <is>
+          <t>https://fr.jooble.org/jdp/7773417443002480443</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AB17"/>
+  <autoFilter ref="A1:AB18"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB3" r:id="rId2"/>
@@ -2265,6 +2367,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB15" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB16" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB18" r:id="rId17"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/cloud_state/offres_suivi.xlsx
+++ b/cloud_state/offres_suivi.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offres" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Offres'!$A$1:$AB$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Offres'!$A$1:$AB$19</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB18"/>
+  <dimension ref="A1:AB19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -2348,8 +2348,104 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-28T11:54:55</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>qTQNr2I8ITv1uApkAAAAAA==</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>JSearch</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Informaticien (H/F)</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Parker Intérim Sens</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Saint-Clément, FR</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>À plein temps</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr"/>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr"/>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr"/>
+      <c r="O19" s="2" t="inlineStr"/>
+      <c r="P19" s="2" t="inlineStr"/>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>Vue.js</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-27T00:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr"/>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>Offre conservee: cible front-end, WordPress, webdesign, UI/UX ou graphisme web.</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>À vérifier</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>À vérifier: score 45/100 grâce à technologies: javascript, vue.js; domaine_metier: wordpress, front-end, ui, ux, design, webdesign, graphisme.</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>technologies=30; titre=0; domaine_metier=15; localisation=0; teletravail=0; contrat=0</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
+          <t>JavaScript, Vue.js</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr"/>
+      <c r="AB19" s="3" t="inlineStr">
+        <is>
+          <t>https://fr.trabajo.org/offre-1911-4733876e9c24ce429a22537da355b585</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AB18"/>
+  <autoFilter ref="A1:AB19"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB3" r:id="rId2"/>
@@ -2368,6 +2464,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB16" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB17" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB19" r:id="rId18"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/cloud_state/offres_suivi.xlsx
+++ b/cloud_state/offres_suivi.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offres" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Offres'!$A$1:$AB$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Offres'!$A$1:$AB$20</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB19"/>
+  <dimension ref="A1:AB20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -2444,8 +2444,116 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-05T11:39:31</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>3451540</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>France Travail</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Ingénieur informatique industrielle (H/F)</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Non specifie</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>21 - Corcelles-lès-Cîteaux</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>21910</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>Débutant accepté</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr"/>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr"/>
+      <c r="O20" s="2" t="inlineStr"/>
+      <c r="P20" s="2" t="inlineStr"/>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>JavaScript</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04T15:51:54.000Z</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04T15:51:54.000Z</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>Offre conservee: cible front-end, WordPress, webdesign, UI/UX ou graphisme web.</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>À vérifier</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>À vérifier: score 51/100 grâce à technologies: javascript, digital, web; domaine_metier: wordpress, front-end, ui, ux, design, webdesign, graphisme; localisation: departement 21; contrat: cdi.</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t>technologies=31; titre=0; domaine_metier=15; localisation=12; teletravail=0; contrat=5; penalites=12</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t>JavaScript</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr"/>
+      <c r="AB20" s="3" t="inlineStr">
+        <is>
+          <t>https://candidat.francetravail.fr/offres/recherche/detail/3451540</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AB19"/>
+  <autoFilter ref="A1:AB20"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB3" r:id="rId2"/>
@@ -2465,6 +2573,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB17" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB18" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB20" r:id="rId19"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/cloud_state/offres_suivi.xlsx
+++ b/cloud_state/offres_suivi.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offres" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Offres'!$A$1:$AB$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Offres'!$A$1:$AB$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB20"/>
+  <dimension ref="A1:AB21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -2552,8 +2552,110 @@
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12T11:56:34</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>-3115163136291784995</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Jooble</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Développeur frontend angular F/H/X</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>PROACTIVE RH - TERTIAIRE ET CADRES</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Dijon</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>Temps plein</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr"/>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>3 170 € a 3 570 €</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="n">
+        <v>3170</v>
+      </c>
+      <c r="L21" s="2" t="n">
+        <v>3570</v>
+      </c>
+      <c r="M21" s="2" t="n">
+        <v>3370</v>
+      </c>
+      <c r="N21" s="2" t="inlineStr"/>
+      <c r="O21" s="2" t="inlineStr"/>
+      <c r="P21" s="2" t="inlineStr"/>
+      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-11T00:00:00.0000000</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr"/>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>Offre conservee: cible front-end, WordPress, webdesign, UI/UX ou graphisme web.</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>À vérifier</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>À vérifier: score 75/100 grâce à technologies: developpeur front-end, front-end; titre: frontend; domaine_metier: wordpress, frontend, front-end, ui, ux, design, webdesign, graphisme; localisation: dijon.</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>technologies=30; titre=15; domaine_metier=15; localisation=15; teletravail=0; contrat=0</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t>developpeur front-end</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr"/>
+      <c r="AB21" s="3" t="inlineStr">
+        <is>
+          <t>https://fr.jooble.org/jdp/-3115163136291784995</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AB20"/>
+  <autoFilter ref="A1:AB21"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB3" r:id="rId2"/>
@@ -2574,6 +2676,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB18" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB19" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB21" r:id="rId20"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/cloud_state/offres_suivi.xlsx
+++ b/cloud_state/offres_suivi.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offres" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Offres'!$A$1:$AB$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Offres'!$A$1:$AB$23</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB21"/>
+  <dimension ref="A1:AB23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -2654,8 +2654,238 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16T13:06:39</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>3781173</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>France Travail</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>UX / UI DESIGNER CONFIRMÉ - H/F</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>ATOL CONSEILS ET DEVELOPPEMENTS</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>21 - Dijon</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>21000</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>2 An(s)</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>Annuel de 35000.0 Euros à 40000.0 Euros</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="n">
+        <v>35000</v>
+      </c>
+      <c r="L22" s="2" t="n">
+        <v>40000</v>
+      </c>
+      <c r="M22" s="2" t="n">
+        <v>37500</v>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>annuel</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr"/>
+      <c r="P22" s="2" t="inlineStr"/>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>UI, UX</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-15T19:33:54.000Z</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-15T19:33:54.000Z</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>Offre conservee: cible front-end, WordPress, webdesign, UI/UX ou graphisme web.</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>Pertinent</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>Pertinent: score 95/100 grâce à technologies: ui designer, ux designer, digital, design, interface, maquette; titre: ui designer, designer; domaine_metier: wordpress, front-end, ui, ux, design, webdesign, graphisme, maquette, interface; localisation: dijon; contrat: cdi.</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>technologies=35; titre=25; domaine_metier=15; localisation=15; teletravail=0; contrat=5</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>UI designer, UX designer</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr"/>
+      <c r="AB22" s="3" t="inlineStr">
+        <is>
+          <t>https://candidat.francetravail.fr/offres/recherche/detail/3781173</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16T13:06:41</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>-2499650368807812898</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Jooble</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Ux / ui designer confirmé - h/f</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>ATOL CONSEILS ET DEVELOPPEMENTS</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Dijon</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>Temps plein</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr"/>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>35k € a 40k €/an</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="n">
+        <v>35000</v>
+      </c>
+      <c r="L23" s="2" t="inlineStr"/>
+      <c r="M23" s="2" t="n">
+        <v>35000</v>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>annuel</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr"/>
+      <c r="P23" s="2" t="inlineStr"/>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>UI, UX</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-15T15:05:11.2594379+00:00</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>Offre conservee: cible front-end, WordPress, webdesign, UI/UX ou graphisme web.</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>Pertinent</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="n">
+        <v>86</v>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>Pertinent: score 86/100 grâce à technologies: ui designer, design, web; titre: ui designer, designer; domaine_metier: wordpress, front-end, ui, ux, design, webdesign, graphisme; localisation: dijon.</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>technologies=31; titre=25; domaine_metier=15; localisation=15; teletravail=0; contrat=0</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>UI designer</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr"/>
+      <c r="AB23" s="3" t="inlineStr">
+        <is>
+          <t>https://fr.jooble.org/jdp/-2499650368807812898</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AB21"/>
+  <autoFilter ref="A1:AB23"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB3" r:id="rId2"/>
@@ -2677,6 +2907,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB19" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB20" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB23" r:id="rId22"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/cloud_state/offres_suivi.xlsx
+++ b/cloud_state/offres_suivi.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offres" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Offres'!$A$1:$AB$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Offres'!$A$1:$AB$24</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB23"/>
+  <dimension ref="A1:AB24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -2884,8 +2884,114 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-07-05T10:32:52</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>NKc6IuVsKmc8xFZNAAAAAA==</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>JSearch</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Tech Lead Front End / Design System (F/H)</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>BPCE Solutions informatiques</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Dijon, FR</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>À plein temps</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>teletravail partiel</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>HTML, CSS, JavaScript, React, Vue.js, Figma, UI, UX</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>2026-06-20T00:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Offre rejetee: devops pur.</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>À vérifier</t>
+        </is>
+      </c>
+      <c r="W24" t="n">
+        <v>55</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>À vérifier: score 55/100 grâce à technologies: frontend, figma, html, css, javascript, react, vue.js, design, design system, web, interface, maquette, accessibilite; titre: front end; domaine_metier: frontend, front end, ui, ux, design, maquette, interface; localisation: dijon; teletravail: teletravail.</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>technologies=35; titre=15; domaine_metier=15; localisation=15; teletravail=10; contrat=0; penalites=35</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>HTML, CSS, JavaScript, React, Vue.js, Figma</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>devops pur</t>
+        </is>
+      </c>
+      <c r="AB24" s="3" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/jobs/view/tech-lead-front-end-design-system-f-h-at-bpce-solutions-informatiques-4378935390</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AB23"/>
+  <autoFilter ref="A1:AB24"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB3" r:id="rId2"/>
@@ -2909,6 +3015,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB21" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB22" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB24" r:id="rId23"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/cloud_state/offres_suivi.xlsx
+++ b/cloud_state/offres_suivi.xlsx
@@ -2915,18 +2915,11 @@
           <t>Dijon, FR</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
           <t>À plein temps</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr">
         <is>
           <t>teletravail partiel</t>
@@ -2945,7 +2938,6 @@
           <t>2026-06-20T00:00:00.000Z</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr"/>
       <c r="T24" t="inlineStr">
         <is>
           <t>Non</t>

--- a/cloud_state/offres_suivi.xlsx
+++ b/cloud_state/offres_suivi.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offres" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Offres'!$A$1:$AB$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Offres'!$A$1:$AB$25</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB24"/>
+  <dimension ref="A1:AB25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -2982,8 +2982,104 @@
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07T11:22:24</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>fh985nbZUZsSuT6VAAAAAA==</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>JSearch</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Spécialiste Informatique Et Nouvelles Technologies</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>ASPIVIX SAS</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>Besançon, FR</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>À plein temps</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr"/>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr"/>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr"/>
+      <c r="O25" s="2" t="inlineStr"/>
+      <c r="P25" s="2" t="inlineStr"/>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>WordPress, HTML, CSS</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02T00:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>Offre conservee: cible front-end, WordPress, webdesign, UI/UX ou graphisme web.</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>À vérifier</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>À vérifier: score 46/100 grâce à technologies: wordpress, html, css, web, accessibilite; domaine_metier: wordpress, front-end, ui, ux, design, webdesign, graphisme; localisation: besancon.</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>technologies=35; titre=0; domaine_metier=15; localisation=8; teletravail=0; contrat=0; penalites=12</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>WordPress, HTML, CSS</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr"/>
+      <c r="AB25" s="3" t="inlineStr">
+        <is>
+          <t>https://fr.trabajo.org/offre-3394-ef81ca7a81e4c07799b8a10490e25fb5</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AB24"/>
+  <autoFilter ref="A1:AB25"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB3" r:id="rId2"/>
@@ -3008,6 +3104,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB22" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB23" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB25" r:id="rId24"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/cloud_state/offres_suivi.xlsx
+++ b/cloud_state/offres_suivi.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offres" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Offres'!$A$1:$AB$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Offres'!$A$1:$AB$26</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB25"/>
+  <dimension ref="A1:AB26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -3078,8 +3078,100 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08T10:33:06</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>8851474125686883999</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Jooble</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>UX / UI Designer confirmé - H/F Ajouter aux favoris</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Non specifie</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Dijon</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr"/>
+      <c r="I26" s="2" t="inlineStr"/>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr"/>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr"/>
+      <c r="O26" s="2" t="inlineStr"/>
+      <c r="P26" s="2" t="inlineStr"/>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>UI, UX</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18T00:00:00.0000000</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>Offre conservee: cible front-end, WordPress, webdesign, UI/UX ou graphisme web.</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>Pertinent</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="n">
+        <v>86</v>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>Pertinent: score 86/100 grâce à technologies: ui designer, design, web; titre: ui designer, designer; domaine_metier: wordpress, front-end, ui, ux, design, webdesign, graphisme; localisation: dijon.</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>technologies=31; titre=25; domaine_metier=15; localisation=15; teletravail=0; contrat=0</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>UI designer</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr"/>
+      <c r="AB26" s="3" t="inlineStr">
+        <is>
+          <t>https://fr.jooble.org/jdp/8851474125686883999</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AB25"/>
+  <autoFilter ref="A1:AB26"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB3" r:id="rId2"/>
@@ -3105,6 +3197,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB23" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB24" r:id="rId23"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB26" r:id="rId25"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/cloud_state/offres_suivi.xlsx
+++ b/cloud_state/offres_suivi.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offres" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Offres'!$A$1:$AB$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Offres'!$A$1:$AB$27</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB26"/>
+  <dimension ref="A1:AB27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -3170,8 +3170,130 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10T11:22:40</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>4780481</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>France Travail</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Développeur informatique senior (H/F)</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Non specifie</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>21 - Dijon</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>21000</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>3 An(s)</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>Annuel de 40000.0 Euros à 50000.0 Euros</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="n">
+        <v>40000</v>
+      </c>
+      <c r="L27" s="2" t="n">
+        <v>50000</v>
+      </c>
+      <c r="M27" s="2" t="n">
+        <v>45000</v>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>annuel</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr"/>
+      <c r="P27" s="2" t="inlineStr"/>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>HTML, CSS, JavaScript</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10T03:20:16.000Z</t>
+        </is>
+      </c>
+      <c r="S27" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10T03:20:16.000Z</t>
+        </is>
+      </c>
+      <c r="T27" s="2" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>Offre conservee: cible front-end, WordPress, webdesign, UI/UX ou graphisme web.</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>À vérifier</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>À vérifier: score 46/100 grâce à technologies: html, css, javascript, web; domaine_metier: wordpress, front-end, ui, ux, design, webdesign, graphisme; localisation: dijon; contrat: cdi.</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>technologies=35; titre=0; domaine_metier=15; localisation=15; teletravail=0; contrat=5; penalites=24</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>HTML, CSS, JavaScript</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr"/>
+      <c r="AB27" s="3" t="inlineStr">
+        <is>
+          <t>https://candidat.francetravail.fr/offres/recherche/detail/4780481</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AB26"/>
+  <autoFilter ref="A1:AB27"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB3" r:id="rId2"/>
@@ -3198,6 +3320,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB24" r:id="rId23"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB25" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB27" r:id="rId26"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/cloud_state/offres_suivi.xlsx
+++ b/cloud_state/offres_suivi.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offres" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Offres'!$A$1:$AB$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Offres'!$A$1:$AB$28</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB27"/>
+  <dimension ref="A1:AB28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -3292,8 +3292,104 @@
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11T09:52:41</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>KkSh9mevU80_kNiVAAAAAA==</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>JSearch</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Responsable Sécurité Informatique (F/H)</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>VEF ICEM Tête de pôle</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>Décines-Charpieu, FR</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>À plein temps</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr"/>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr"/>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr"/>
+      <c r="O28" s="2" t="inlineStr"/>
+      <c r="P28" s="2" t="inlineStr"/>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>Vue.js</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10T00:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>Offre conservee: cible front-end, WordPress, webdesign, UI/UX ou graphisme web.</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>À vérifier</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>À vérifier: score 50/100 grâce à technologies: javascript, vue.js, design; domaine_metier: wordpress, front-end, ui, ux, design, webdesign, graphisme.</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>technologies=35; titre=0; domaine_metier=15; localisation=0; teletravail=0; contrat=0</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>JavaScript, Vue.js</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr"/>
+      <c r="AB28" s="3" t="inlineStr">
+        <is>
+          <t>https://taleez.com/apply/pole-information-security-officer-piso-f-h-decines-charpieu-vef-icem-tete-de-pole-cdi</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AB27"/>
+  <autoFilter ref="A1:AB28"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB3" r:id="rId2"/>
@@ -3321,6 +3417,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB25" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB26" r:id="rId25"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB28" r:id="rId27"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/cloud_state/offres_suivi.xlsx
+++ b/cloud_state/offres_suivi.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offres" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Offres'!$A$1:$AB$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Offres'!$A$1:$AB$29</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB28"/>
+  <dimension ref="A1:AB29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -3388,8 +3388,104 @@
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-12T10:04:55</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>kKm_w0UgGXLpHMLxAAAAAA==</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>JSearch</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Administrateur exploitation informatique F/H</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>La Poste Groupe</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>Dijon, FR</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>À plein temps</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr"/>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr"/>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr"/>
+      <c r="O29" s="2" t="inlineStr"/>
+      <c r="P29" s="2" t="inlineStr"/>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>Vue.js</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16T00:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>Offre conservee: cible front-end, WordPress, webdesign, UI/UX ou graphisme web.</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>À vérifier</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>À vérifier: score 60/100 grâce à technologies: javascript, vue.js; domaine_metier: wordpress, front-end, ui, ux, design, webdesign, graphisme; localisation: dijon.</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>technologies=30; titre=0; domaine_metier=15; localisation=15; teletravail=0; contrat=0</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>JavaScript, Vue.js</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr"/>
+      <c r="AB29" s="3" t="inlineStr">
+        <is>
+          <t>https://www.welcometothejungle.com/fr/companies/la-poste-groupe/jobs/administrateur-exploitation-informatique-f-h_dijon</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AB28"/>
+  <autoFilter ref="A1:AB29"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB3" r:id="rId2"/>
@@ -3418,6 +3514,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB26" r:id="rId25"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB27" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB29" r:id="rId28"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/cloud_state/offres_suivi.xlsx
+++ b/cloud_state/offres_suivi.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offres" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Offres'!$A$1:$AB$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Offres'!$A$1:$AB$30</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB29"/>
+  <dimension ref="A1:AB30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -3484,8 +3484,116 @@
         </is>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18T09:50:12</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>5100389</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>France Travail</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>DÉVELOPPEUR WEB FULL STACK - H/F</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Altagile</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>21 - Dijon</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>21000</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>2 An(s)</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr"/>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr"/>
+      <c r="O30" s="2" t="inlineStr"/>
+      <c r="P30" s="2" t="inlineStr"/>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>JavaScript, React</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-17T19:33:46.000Z</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-17T19:33:46.000Z</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>Offre conservee: cible front-end, WordPress, webdesign, UI/UX ou graphisme web.</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>À vérifier</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>À vérifier: score 70/100 grâce à technologies: javascript, react, web; domaine_metier: wordpress, front-end, ui, ux, design, webdesign, graphisme; localisation: dijon; contrat: cdi.</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>technologies=35; titre=0; domaine_metier=15; localisation=15; teletravail=0; contrat=5</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>JavaScript, React</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr"/>
+      <c r="AB30" s="3" t="inlineStr">
+        <is>
+          <t>https://candidat.francetravail.fr/offres/recherche/detail/5100389</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AB29"/>
+  <autoFilter ref="A1:AB30"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB3" r:id="rId2"/>
@@ -3515,6 +3623,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB27" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB28" r:id="rId27"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB30" r:id="rId29"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/cloud_state/offres_suivi.xlsx
+++ b/cloud_state/offres_suivi.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offres" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Offres'!$A$1:$AB$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Offres'!$A$1:$AB$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB30"/>
+  <dimension ref="A1:AB31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -3592,8 +3592,116 @@
         </is>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T09:19:05</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>-8482257207862652955</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Jooble</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Ux / ui designer - h/f</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>ATOL CONSEILS ET DEVELOPPEMENTS</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>Dijon</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>Temps plein</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr"/>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>35k € a 40k €/an</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="n">
+        <v>35000</v>
+      </c>
+      <c r="L31" s="2" t="inlineStr"/>
+      <c r="M31" s="2" t="n">
+        <v>35000</v>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>annuel</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr"/>
+      <c r="P31" s="2" t="inlineStr"/>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>UI, UX</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06T15:05:12.0440755+00:00</t>
+        </is>
+      </c>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>Offre conservee: cible front-end, WordPress, webdesign, UI/UX ou graphisme web.</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>Pertinent</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="n">
+        <v>86</v>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>Pertinent: score 86/100 grâce à technologies: ui designer, design, web; titre: ui designer, designer; domaine_metier: wordpress, front-end, ui, ux, design, webdesign, graphisme; localisation: dijon.</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>technologies=31; titre=25; domaine_metier=15; localisation=15; teletravail=0; contrat=0</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>UI designer</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr"/>
+      <c r="AB31" s="3" t="inlineStr">
+        <is>
+          <t>https://fr.jooble.org/jdp/-8482257207862652955</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AB30"/>
+  <autoFilter ref="A1:AB31"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB3" r:id="rId2"/>
@@ -3624,6 +3732,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB28" r:id="rId27"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB29" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB31" r:id="rId30"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/cloud_state/offres_suivi.xlsx
+++ b/cloud_state/offres_suivi.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offres" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Offres'!$A$1:$AB$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Offres'!$A$1:$AB$32</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB31"/>
+  <dimension ref="A1:AB32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -3700,8 +3700,116 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-14T09:31:26</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>4591837520519648886</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Jooble</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Ux - Ui Designer H/F</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Atol Conseils et développements</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>Dijon</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>Temps plein</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr"/>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>35k € a 40k €/an</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="n">
+        <v>35000</v>
+      </c>
+      <c r="L32" s="2" t="inlineStr"/>
+      <c r="M32" s="2" t="n">
+        <v>35000</v>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>annuel</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr"/>
+      <c r="P32" s="2" t="inlineStr"/>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>UI, UX</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09T00:00:00.0000000</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>Offre conservee: cible front-end, WordPress, webdesign, UI/UX ou graphisme web.</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>Pertinent</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>Pertinent: score 90/100 grâce à technologies: ui designer, design, interface, maquette; titre: ui designer, designer; domaine_metier: wordpress, front-end, ui, ux, design, webdesign, graphisme, maquette, interface; localisation: dijon.</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>technologies=35; titre=25; domaine_metier=15; localisation=15; teletravail=0; contrat=0</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>UI designer</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr"/>
+      <c r="AB32" s="3" t="inlineStr">
+        <is>
+          <t>https://fr.jooble.org/desc/4591837520519648886</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AB31"/>
+  <autoFilter ref="A1:AB32"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB3" r:id="rId2"/>
@@ -3733,6 +3841,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB29" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB30" r:id="rId29"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB32" r:id="rId31"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/cloud_state/offres_suivi.xlsx
+++ b/cloud_state/offres_suivi.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offres" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Offres'!$A$1:$AB$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Offres'!$A$1:$AB$33</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB32"/>
+  <dimension ref="A1:AB33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -3808,8 +3808,104 @@
         </is>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20T09:00:17</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>MGlCVjVIbWpHeTJQQ095dUFBQUFBQT09OkVzd0JDb3dCUVVwcFZEUjBTbDlUVGxkeE9Xc3pVMXB4UlVwUVJERkJUazk1V1VOQloyOUtZVXRMZEdneVlrUmthRWhsYm1kVFdtdEpZMDlITkdKMk5qRlJjbFJwV1VkUmIzbGtTRXBwTTJkNFJYcE9aSEZXZVU5dFVUTkJSMFl5TFZkWWExaEdXamRYYjFoTmFqTnRaVFZTYmtOMU1sOUVTMFV4TW1GUFZGTmFVV2RaTXpBMVVGWjJiMjVUTVRGSVNFSVNGMGc0UzBkaGRUWnpSMHN5UjNkaWExQXRTVU5DZDBGUkdpSkJSSE55T1daVFVuRkdSVk5qYVRaTE16WjVZVVZ0UzNFNWJUQkZPVGhhVEdKMw</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>JSearch</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>DÉVELOPPEUR WEB FULL STACK</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Altagile</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>Dijon, FR</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>À plein temps</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr"/>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr"/>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr"/>
+      <c r="O33" s="2" t="inlineStr"/>
+      <c r="P33" s="2" t="inlineStr"/>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>JavaScript, React</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-19T00:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>Offre conservee: cible front-end, WordPress, webdesign, UI/UX ou graphisme web.</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>À vérifier</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>À vérifier: score 65/100 grâce à technologies: javascript, react, web; domaine_metier: wordpress, front-end, ui, ux, design, webdesign, graphisme; localisation: dijon.</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>technologies=35; titre=0; domaine_metier=15; localisation=15; teletravail=0; contrat=0</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>JavaScript, React</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr"/>
+      <c r="AB33" s="3" t="inlineStr">
+        <is>
+          <t>https://fr.trabajo.org/offre-4025-e98da66ec1bd1837e444a5967f239d4c</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AB32"/>
+  <autoFilter ref="A1:AB33"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB3" r:id="rId2"/>
@@ -3842,6 +3938,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB30" r:id="rId29"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB31" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB33" r:id="rId32"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/cloud_state/offres_suivi.xlsx
+++ b/cloud_state/offres_suivi.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offres" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Offres'!$A$1:$AB$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Offres'!$A$1:$AB$34</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB33"/>
+  <dimension ref="A1:AB34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -3904,8 +3904,104 @@
         </is>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-21T09:02:42</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>MGlCVjVIbWpHeTJQQ095dUFBQUFBQT09OkVzd0JDb3dCUVVwcFZEUjBTM2R1U21veVN6RmhOVWQ1TjI4MGRrUk9TVkY1V1Rkdk9IQm9SVEZEUmtSdFQwWkNOek4zZWtVMlFXMXZZVEF0VnpKUWJWODRlVXB3TlZOeFIzaGpZbFYwYkdaTk5EbFNRMmc0YWxKbGIwWjRWSEpYT1dsdlZIRk9lbk5rT0ZCcVEzZzRSM0JvVEZaclFsQnBkRFkxZUU1TWVrNWpkRTFsY0ZoNGNVWkpWbkpZWmpCTmNsUVNGMDFDVTBsaGRUTmZRMlZEZUhjNFkxQnBYMTlNTWtGRkdpSkJSSE55T1daUlQwd3dOVEptUjNWRVF6QTBSWHBzVW1ONFVVWlpaVXRLZWxKMw</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>JSearch</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>DÉVELOPPEUR WEB FULL STACK</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Altagile</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>Dijon, FR</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>À plein temps</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr"/>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr"/>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr"/>
+      <c r="O34" s="2" t="inlineStr"/>
+      <c r="P34" s="2" t="inlineStr"/>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>JavaScript, React</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-19T00:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>Offre conservee: cible front-end, WordPress, webdesign, UI/UX ou graphisme web.</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>À vérifier</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>À vérifier: score 65/100 grâce à technologies: javascript, react, web; domaine_metier: wordpress, front-end, ui, ux, design, webdesign, graphisme; localisation: dijon.</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>technologies=35; titre=0; domaine_metier=15; localisation=15; teletravail=0; contrat=0</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>JavaScript, React</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr"/>
+      <c r="AB34" s="3" t="inlineStr">
+        <is>
+          <t>https://fr.trabajo.org/offre-4025-e98da66ec1bd1837e444a5967f239d4c</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AB33"/>
+  <autoFilter ref="A1:AB34"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB3" r:id="rId2"/>
@@ -3939,6 +4035,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB31" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB32" r:id="rId31"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB34" r:id="rId33"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/cloud_state/offres_suivi.xlsx
+++ b/cloud_state/offres_suivi.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offres" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Offres'!$A$1:$AB$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Offres'!$A$1:$AB$35</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB34"/>
+  <dimension ref="A1:AB35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4000,8 +4000,100 @@
         </is>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03T12:53:57</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>8641078399681164805</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Jooble</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>UX / UI Designer - H/F Ajouter aux favoris</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>Non specifie</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>Dijon</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr"/>
+      <c r="I35" s="2" t="inlineStr"/>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr"/>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr"/>
+      <c r="O35" s="2" t="inlineStr"/>
+      <c r="P35" s="2" t="inlineStr"/>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>UI, UX</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11T00:00:00.0000000</t>
+        </is>
+      </c>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>Offre conservee: cible front-end, WordPress, webdesign, UI/UX ou graphisme web.</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>Pertinent</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="n">
+        <v>86</v>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>Pertinent: score 86/100 grâce à technologies: ui designer, design, web; titre: ui designer, designer; domaine_metier: wordpress, front-end, ui, ux, design, webdesign, graphisme; localisation: dijon.</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>technologies=31; titre=25; domaine_metier=15; localisation=15; teletravail=0; contrat=0</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>UI designer</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr"/>
+      <c r="AB35" s="3" t="inlineStr">
+        <is>
+          <t>https://fr.jooble.org/jdp/8641078399681164805</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AB34"/>
+  <autoFilter ref="A1:AB35"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB3" r:id="rId2"/>
@@ -4036,6 +4128,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB32" r:id="rId31"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB33" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB35" r:id="rId34"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/cloud_state/offres_suivi.xlsx
+++ b/cloud_state/offres_suivi.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offres" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Offres'!$A$1:$AB$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Offres'!$A$1:$AB$36</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB35"/>
+  <dimension ref="A1:AB36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -448,7 +448,7 @@
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
     <col width="36" customWidth="1" min="5" max="5"/>
-    <col width="28" customWidth="1" min="6" max="6"/>
+    <col width="36" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="25" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
@@ -4092,8 +4092,104 @@
         </is>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-06T12:12:43</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>YmluZzotMTU5NDg4MDY4MS5SZXRybw</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>JSearch</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Administrateur Exploitation Informatique F/H</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Le Groupe La Poste</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>Dijon, Bourgogne-Franche-Comté, FR</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>Temps plein</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr"/>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr"/>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr"/>
+      <c r="O36" s="2" t="inlineStr"/>
+      <c r="P36" s="2" t="inlineStr"/>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>Vue.js</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16T00:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>Offre conservee: cible front-end, WordPress, webdesign, UI/UX ou graphisme web.</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>À vérifier</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>À vérifier: score 60/100 grâce à technologies: javascript, vue.js; domaine_metier: wordpress, front-end, ui, ux, design, webdesign, graphisme; localisation: dijon.</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>technologies=30; titre=0; domaine_metier=15; localisation=15; teletravail=0; contrat=0</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>JavaScript, Vue.js</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr"/>
+      <c r="AB36" s="3" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.fr/job-listing/administrateur-exploitation-informatique-f-h-la-poste-JV_IC3069836_KO0,44_KE45,53.htm?jl=1010169308272&amp;trk=bingjobs</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AB35"/>
+  <autoFilter ref="A1:AB36"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB3" r:id="rId2"/>
@@ -4129,6 +4225,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB33" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB34" r:id="rId33"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB36" r:id="rId35"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/cloud_state/offres_suivi.xlsx
+++ b/cloud_state/offres_suivi.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offres" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Offres'!$A$1:$AB$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Offres'!$A$1:$AB$37</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB36"/>
+  <dimension ref="A1:AB37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4188,8 +4188,104 @@
         </is>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-10T12:59:08</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>-8448818426060558382</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Jooble</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Conseiller(ère) informatique support client</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>SG2i</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>Saint-Apollinaire, Côte-d'Or</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>Intérimaire</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr"/>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr"/>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr"/>
+      <c r="O37" s="2" t="inlineStr"/>
+      <c r="P37" s="2" t="inlineStr"/>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>Vue.js</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-01T22:46:39.0151570+00:00</t>
+        </is>
+      </c>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>Offre conservee: cible front-end, WordPress, webdesign, UI/UX ou graphisme web.</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>À vérifier</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>À vérifier: score 60/100 grâce à technologies: javascript, vue.js; domaine_metier: wordpress, front-end, ui, ux, design, webdesign, graphisme; localisation: saint-apollinaire.</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>technologies=30; titre=0; domaine_metier=15; localisation=15; teletravail=0; contrat=0</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>JavaScript, Vue.js</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr"/>
+      <c r="AB37" s="3" t="inlineStr">
+        <is>
+          <t>https://fr.jooble.org/jdp/-8448818426060558382</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AB36"/>
+  <autoFilter ref="A1:AB37"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB3" r:id="rId2"/>
@@ -4226,6 +4322,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB34" r:id="rId33"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB35" r:id="rId34"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB37" r:id="rId36"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
